--- a/Code and data/Final data/Sensitivity_Analysis.xlsx
+++ b/Code and data/Final data/Sensitivity_Analysis.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -373,7 +373,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.9254</v>
+        <v>0.9341</v>
       </c>
     </row>
     <row r="3">
@@ -383,7 +383,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.9868</v>
+        <v>0.9855</v>
       </c>
     </row>
     <row r="4">
@@ -403,7 +403,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.9923999999999999</v>
+        <v>0.9896</v>
       </c>
     </row>
     <row r="6">
@@ -413,7 +413,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.9782</v>
+        <v>0.9661</v>
       </c>
     </row>
     <row r="7">
@@ -423,7 +423,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.9607</v>
+        <v>0.9876</v>
       </c>
     </row>
     <row r="8">
@@ -433,7 +433,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.98</v>
+        <v>0.956</v>
       </c>
     </row>
     <row r="9">
@@ -443,77 +443,97 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.9926</v>
+        <v>0.9835</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Drop Vuln_Finance</t>
+          <t>Drop Vuln_Supply_Chain</t>
         </is>
       </c>
       <c r="B10">
-        <v>0.951</v>
+        <v>0.9883</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Drop Vuln_Supply_Chain</t>
+          <t>Drop Vuln_Technology</t>
         </is>
       </c>
       <c r="B11">
-        <v>0.9912</v>
+        <v>0.9697</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Drop Vuln_Technology</t>
+          <t>Drop Vuln_Institutions</t>
         </is>
       </c>
       <c r="B12">
-        <v>0.9819</v>
+        <v>0.9681999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Drop Vuln_Institutions</t>
+          <t>Drop Vuln_Diversification</t>
         </is>
       </c>
       <c r="B13">
-        <v>0.9871</v>
+        <v>0.9821</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Drop Vuln_Diversification</t>
+          <t>Arithmetic mean</t>
         </is>
       </c>
       <c r="B14">
-        <v>0.9961</v>
+        <v>0.786</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Arithmetic mean</t>
+          <t>Z-score normalization</t>
         </is>
       </c>
       <c r="B15">
-        <v>0.6483</v>
+        <v>0.9831</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Z-score normalization</t>
+          <t>EDGAR Scope1 [C19-C20]</t>
         </is>
       </c>
       <c r="B16">
-        <v>0.9912</v>
+        <v>0.9509</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EDGAR Scope1 [C23]</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>0.9496</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EDGAR Scope1 [C24]</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>0.9594</v>
       </c>
     </row>
   </sheetData>

--- a/Code and data/Final data/Sensitivity_Analysis.xlsx
+++ b/Code and data/Final data/Sensitivity_Analysis.xlsx
@@ -7,7 +7,9 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="baseline_battery" sheetId="1" r:id="rId1"/>
+    <sheet name="carbon_cost_tri" sheetId="2" r:id="rId2"/>
+    <sheet name="phase_in_trajectory" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,7 +364,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>spearman_rho</t>
+          <t>rho_pooled</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>rho_within_sector</t>
         </is>
       </c>
     </row>
@@ -375,6 +382,9 @@
       <c r="B2">
         <v>0.9341</v>
       </c>
+      <c r="C2">
+        <v>0.93</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -385,6 +395,9 @@
       <c r="B3">
         <v>0.9855</v>
       </c>
+      <c r="C3">
+        <v>0.984</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -395,6 +408,9 @@
       <c r="B4">
         <v>1</v>
       </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -405,6 +421,9 @@
       <c r="B5">
         <v>0.9896</v>
       </c>
+      <c r="C5">
+        <v>0.9886</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -415,6 +434,9 @@
       <c r="B6">
         <v>0.9661</v>
       </c>
+      <c r="C6">
+        <v>0.9631</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -425,6 +447,9 @@
       <c r="B7">
         <v>0.9876</v>
       </c>
+      <c r="C7">
+        <v>0.9911</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -435,6 +460,9 @@
       <c r="B8">
         <v>0.956</v>
       </c>
+      <c r="C8">
+        <v>0.9601</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -445,6 +473,9 @@
       <c r="B9">
         <v>0.9835</v>
       </c>
+      <c r="C9">
+        <v>0.9821</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -455,6 +486,9 @@
       <c r="B10">
         <v>0.9883</v>
       </c>
+      <c r="C10">
+        <v>0.9908</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -465,6 +499,9 @@
       <c r="B11">
         <v>0.9697</v>
       </c>
+      <c r="C11">
+        <v>0.9696</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -475,6 +512,9 @@
       <c r="B12">
         <v>0.9681999999999999</v>
       </c>
+      <c r="C12">
+        <v>0.9615</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -485,6 +525,9 @@
       <c r="B13">
         <v>0.9821</v>
       </c>
+      <c r="C13">
+        <v>0.9846</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -495,6 +538,9 @@
       <c r="B14">
         <v>0.786</v>
       </c>
+      <c r="C14">
+        <v>0.7792</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -505,6 +551,9 @@
       <c r="B15">
         <v>0.9831</v>
       </c>
+      <c r="C15">
+        <v>0.9874000000000001</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -515,6 +564,9 @@
       <c r="B16">
         <v>0.9509</v>
       </c>
+      <c r="C16">
+        <v>0.9509</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -525,6 +577,9 @@
       <c r="B17">
         <v>0.9496</v>
       </c>
+      <c r="C17">
+        <v>0.9496</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -534,6 +589,273 @@
       </c>
       <c r="B18">
         <v>0.9594</v>
+      </c>
+      <c r="C18">
+        <v>0.9594</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>rho_pooled</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>rho_within_sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Cost TRI vs emissions-baseline TRI</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.5326</v>
+      </c>
+      <c r="C2">
+        <v>0.6342</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Cost TRI norm: minmax vs log</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.8275</v>
+      </c>
+      <c r="C3">
+        <v>0.8195</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Cost TRI norm: minmax vs rank</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.8889</v>
+      </c>
+      <c r="C4">
+        <v>0.8369</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Cost TRI: 2034 headline vs 2024 policy state</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.9109</v>
+      </c>
+      <c r="C5">
+        <v>0.8939</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>free_alloc</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>CBAM_factor</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>cost_EURbn</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ETS_share</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>n_priced</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>rho_vs_2034</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>2024</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>2.1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>339</v>
+      </c>
+      <c r="G2">
+        <v>0.911</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2026</v>
+      </c>
+      <c r="B3">
+        <v>0.975</v>
+      </c>
+      <c r="C3">
+        <v>0.025</v>
+      </c>
+      <c r="D3">
+        <v>3.1</v>
+      </c>
+      <c r="E3">
+        <v>0.87</v>
+      </c>
+      <c r="F3">
+        <v>2224</v>
+      </c>
+      <c r="G3">
+        <v>0.929</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>2028</v>
+      </c>
+      <c r="B4">
+        <v>0.9</v>
+      </c>
+      <c r="C4">
+        <v>0.1</v>
+      </c>
+      <c r="D4">
+        <v>6.2</v>
+      </c>
+      <c r="E4">
+        <v>0.73</v>
+      </c>
+      <c r="F4">
+        <v>2224</v>
+      </c>
+      <c r="G4">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2030</v>
+      </c>
+      <c r="B5">
+        <v>0.515</v>
+      </c>
+      <c r="C5">
+        <v>0.485</v>
+      </c>
+      <c r="D5">
+        <v>22.1</v>
+      </c>
+      <c r="E5">
+        <v>0.63</v>
+      </c>
+      <c r="F5">
+        <v>2224</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>2032</v>
+      </c>
+      <c r="B6">
+        <v>0.265</v>
+      </c>
+      <c r="C6">
+        <v>0.735</v>
+      </c>
+      <c r="D6">
+        <v>32.4</v>
+      </c>
+      <c r="E6">
+        <v>0.62</v>
+      </c>
+      <c r="F6">
+        <v>2224</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>2034</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>43.3</v>
+      </c>
+      <c r="E7">
+        <v>0.61</v>
+      </c>
+      <c r="F7">
+        <v>2224</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Code and data/Final data/Sensitivity_Analysis.xlsx
+++ b/Code and data/Final data/Sensitivity_Analysis.xlsx
@@ -601,7 +601,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -671,6 +671,19 @@
       </c>
       <c r="C5">
         <v>0.8939</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Cost TRI CBAM intensity: direct vs embodied</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.9913999999999999</v>
+      </c>
+      <c r="C6">
+        <v>0.9947</v>
       </c>
     </row>
   </sheetData>

--- a/Code and data/Final data/Sensitivity_Analysis.xlsx
+++ b/Code and data/Final data/Sensitivity_Analysis.xlsx
@@ -8,8 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="baseline_battery" sheetId="1" r:id="rId1"/>
-    <sheet name="carbon_cost_tri" sheetId="2" r:id="rId2"/>
-    <sheet name="phase_in_trajectory" sheetId="3" r:id="rId3"/>
+    <sheet name="risk_tri" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -380,10 +379,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.9341</v>
+        <v>0.9351</v>
       </c>
       <c r="C2">
-        <v>0.93</v>
+        <v>0.9344</v>
       </c>
     </row>
     <row r="3">
@@ -396,7 +395,7 @@
         <v>0.9855</v>
       </c>
       <c r="C3">
-        <v>0.984</v>
+        <v>0.9847</v>
       </c>
     </row>
     <row r="4">
@@ -422,7 +421,7 @@
         <v>0.9896</v>
       </c>
       <c r="C5">
-        <v>0.9886</v>
+        <v>0.9879</v>
       </c>
     </row>
     <row r="6">
@@ -432,10 +431,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.9661</v>
+        <v>0.9663</v>
       </c>
       <c r="C6">
-        <v>0.9631</v>
+        <v>0.9612000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -445,10 +444,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.9876</v>
+        <v>0.9929</v>
       </c>
       <c r="C7">
-        <v>0.9911</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="8">
@@ -458,10 +457,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.956</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="C8">
-        <v>0.9601</v>
+        <v>0.978</v>
       </c>
     </row>
     <row r="9">
@@ -471,10 +470,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.9835</v>
+        <v>0.9823</v>
       </c>
       <c r="C9">
-        <v>0.9821</v>
+        <v>0.9816</v>
       </c>
     </row>
     <row r="10">
@@ -484,10 +483,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.9883</v>
+        <v>0.984</v>
       </c>
       <c r="C10">
-        <v>0.9908</v>
+        <v>0.9887</v>
       </c>
     </row>
     <row r="11">
@@ -497,10 +496,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.9697</v>
+        <v>0.9571</v>
       </c>
       <c r="C11">
-        <v>0.9696</v>
+        <v>0.9554</v>
       </c>
     </row>
     <row r="12">
@@ -510,10 +509,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.9681999999999999</v>
+        <v>0.9701</v>
       </c>
       <c r="C12">
-        <v>0.9615</v>
+        <v>0.9635</v>
       </c>
     </row>
     <row r="13">
@@ -523,10 +522,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.9821</v>
+        <v>0.9864000000000001</v>
       </c>
       <c r="C13">
-        <v>0.9846</v>
+        <v>0.9871</v>
       </c>
     </row>
     <row r="14">
@@ -536,10 +535,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.786</v>
+        <v>0.7967</v>
       </c>
       <c r="C14">
-        <v>0.7792</v>
+        <v>0.7835</v>
       </c>
     </row>
     <row r="15">
@@ -549,10 +548,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.9831</v>
+        <v>0.9825</v>
       </c>
       <c r="C15">
-        <v>0.9874000000000001</v>
+        <v>0.9869</v>
       </c>
     </row>
     <row r="16">
@@ -562,10 +561,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.9509</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="C16">
-        <v>0.9509</v>
+        <v>0.9419999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -575,10 +574,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.9496</v>
+        <v>0.9342</v>
       </c>
       <c r="C17">
-        <v>0.9496</v>
+        <v>0.9342</v>
       </c>
     </row>
     <row r="18">
@@ -588,10 +587,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.9594</v>
+        <v>0.9613</v>
       </c>
       <c r="C18">
-        <v>0.9594</v>
+        <v>0.9613</v>
       </c>
     </row>
   </sheetData>
@@ -624,251 +623,66 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cost TRI vs emissions-baseline TRI</t>
+          <t>Headline TRI vs raw-emissions TRI</t>
         </is>
       </c>
       <c r="B2">
-        <v>0.5326</v>
+        <v>0.5957</v>
       </c>
       <c r="C2">
-        <v>0.6342</v>
+        <v>0.7167</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cost TRI norm: minmax vs log</t>
+          <t>Headline TRI norm: minmax vs log</t>
         </is>
       </c>
       <c r="B3">
-        <v>0.8275</v>
+        <v>0.8387</v>
       </c>
       <c r="C3">
-        <v>0.8195</v>
+        <v>0.8395</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cost TRI norm: minmax vs rank</t>
+          <t>Headline TRI norm: minmax vs rank</t>
         </is>
       </c>
       <c r="B4">
-        <v>0.8889</v>
+        <v>0.8801</v>
       </c>
       <c r="C4">
-        <v>0.8369</v>
+        <v>0.8205</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cost TRI: 2034 headline vs 2024 policy state</t>
+          <t>Headline TRI CBAM intensity: direct vs embodied</t>
         </is>
       </c>
       <c r="B5">
-        <v>0.9109</v>
+        <v>0.9887</v>
       </c>
       <c r="C5">
-        <v>0.8939</v>
+        <v>0.9919</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cost TRI CBAM intensity: direct vs embodied</t>
+          <t>Headline TRI CBAM allocation: employment-only vs plant-emission hybrid</t>
         </is>
       </c>
       <c r="B6">
-        <v>0.9913999999999999</v>
+        <v>0.9746</v>
       </c>
       <c r="C6">
-        <v>0.9947</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>free_alloc</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>CBAM_factor</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>cost_EURbn</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>ETS_share</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>n_priced</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rho_vs_2034</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
-        <v>2024</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>2.1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>339</v>
-      </c>
-      <c r="G2">
-        <v>0.911</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>2026</v>
-      </c>
-      <c r="B3">
-        <v>0.975</v>
-      </c>
-      <c r="C3">
-        <v>0.025</v>
-      </c>
-      <c r="D3">
-        <v>3.1</v>
-      </c>
-      <c r="E3">
-        <v>0.87</v>
-      </c>
-      <c r="F3">
-        <v>2224</v>
-      </c>
-      <c r="G3">
-        <v>0.929</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <v>2028</v>
-      </c>
-      <c r="B4">
-        <v>0.9</v>
-      </c>
-      <c r="C4">
-        <v>0.1</v>
-      </c>
-      <c r="D4">
-        <v>6.2</v>
-      </c>
-      <c r="E4">
-        <v>0.73</v>
-      </c>
-      <c r="F4">
-        <v>2224</v>
-      </c>
-      <c r="G4">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5">
-        <v>2030</v>
-      </c>
-      <c r="B5">
-        <v>0.515</v>
-      </c>
-      <c r="C5">
-        <v>0.485</v>
-      </c>
-      <c r="D5">
-        <v>22.1</v>
-      </c>
-      <c r="E5">
-        <v>0.63</v>
-      </c>
-      <c r="F5">
-        <v>2224</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>2032</v>
-      </c>
-      <c r="B6">
-        <v>0.265</v>
-      </c>
-      <c r="C6">
-        <v>0.735</v>
-      </c>
-      <c r="D6">
-        <v>32.4</v>
-      </c>
-      <c r="E6">
-        <v>0.62</v>
-      </c>
-      <c r="F6">
-        <v>2224</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <v>2034</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>43.3</v>
-      </c>
-      <c r="E7">
-        <v>0.61</v>
-      </c>
-      <c r="F7">
-        <v>2224</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
+        <v>0.988</v>
       </c>
     </row>
   </sheetData>

--- a/Code and data/Final data/Sensitivity_Analysis.xlsx
+++ b/Code and data/Final data/Sensitivity_Analysis.xlsx
@@ -379,10 +379,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.9351</v>
+        <v>0.9364</v>
       </c>
       <c r="C2">
-        <v>0.9344</v>
+        <v>0.9366</v>
       </c>
     </row>
     <row r="3">
@@ -392,10 +392,10 @@
         </is>
       </c>
       <c r="B3">
+        <v>0.9862</v>
+      </c>
+      <c r="C3">
         <v>0.9855</v>
-      </c>
-      <c r="C3">
-        <v>0.9847</v>
       </c>
     </row>
     <row r="4">
@@ -418,10 +418,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.9896</v>
+        <v>0.9902</v>
       </c>
       <c r="C5">
-        <v>0.9879</v>
+        <v>0.9888</v>
       </c>
     </row>
     <row r="6">
@@ -431,10 +431,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.9663</v>
+        <v>0.969</v>
       </c>
       <c r="C6">
-        <v>0.9612000000000001</v>
+        <v>0.9641</v>
       </c>
     </row>
     <row r="7">
@@ -444,10 +444,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.9929</v>
+        <v>0.9903999999999999</v>
       </c>
       <c r="C7">
-        <v>0.995</v>
+        <v>0.9947</v>
       </c>
     </row>
     <row r="8">
@@ -457,10 +457,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.9752999999999999</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="C8">
-        <v>0.978</v>
+        <v>0.9756</v>
       </c>
     </row>
     <row r="9">
@@ -470,10 +470,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.9823</v>
+        <v>0.9845</v>
       </c>
       <c r="C9">
-        <v>0.9816</v>
+        <v>0.9827</v>
       </c>
     </row>
     <row r="10">
@@ -483,10 +483,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.984</v>
+        <v>0.9858</v>
       </c>
       <c r="C10">
-        <v>0.9887</v>
+        <v>0.9903</v>
       </c>
     </row>
     <row r="11">
@@ -496,10 +496,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.9571</v>
+        <v>0.9634</v>
       </c>
       <c r="C11">
-        <v>0.9554</v>
+        <v>0.9654</v>
       </c>
     </row>
     <row r="12">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.9701</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="C12">
-        <v>0.9635</v>
+        <v>0.9641999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.9864000000000001</v>
+        <v>0.9877</v>
       </c>
       <c r="C13">
-        <v>0.9871</v>
+        <v>0.9885</v>
       </c>
     </row>
     <row r="14">
@@ -535,10 +535,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.7967</v>
+        <v>0.7944</v>
       </c>
       <c r="C14">
-        <v>0.7835</v>
+        <v>0.782</v>
       </c>
     </row>
     <row r="15">
@@ -548,10 +548,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.9825</v>
+        <v>0.9849</v>
       </c>
       <c r="C15">
-        <v>0.9869</v>
+        <v>0.9871</v>
       </c>
     </row>
     <row r="16">
@@ -561,10 +561,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.9419999999999999</v>
+        <v>0.9421</v>
       </c>
       <c r="C16">
-        <v>0.9419999999999999</v>
+        <v>0.9421</v>
       </c>
     </row>
     <row r="17">
@@ -574,10 +574,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.9342</v>
+        <v>0.9305</v>
       </c>
       <c r="C17">
-        <v>0.9342</v>
+        <v>0.9305</v>
       </c>
     </row>
     <row r="18">
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.9613</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="C18">
-        <v>0.9613</v>
+        <v>0.9602000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -627,10 +627,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.5957</v>
+        <v>0.5111</v>
       </c>
       <c r="C2">
-        <v>0.7167</v>
+        <v>0.655</v>
       </c>
     </row>
     <row r="3">
@@ -640,10 +640,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.8387</v>
+        <v>0.845</v>
       </c>
       <c r="C3">
-        <v>0.8395</v>
+        <v>0.8237</v>
       </c>
     </row>
     <row r="4">
@@ -653,10 +653,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.8801</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="C4">
-        <v>0.8205</v>
+        <v>0.7927999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -666,10 +666,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.9887</v>
+        <v>0.9866</v>
       </c>
       <c r="C5">
-        <v>0.9919</v>
+        <v>0.9902</v>
       </c>
     </row>
     <row r="6">
@@ -679,10 +679,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.9746</v>
+        <v>0.9752</v>
       </c>
       <c r="C6">
-        <v>0.988</v>
+        <v>0.9871</v>
       </c>
     </row>
   </sheetData>

--- a/Code and data/Final data/Sensitivity_Analysis.xlsx
+++ b/Code and data/Final data/Sensitivity_Analysis.xlsx
@@ -382,7 +382,7 @@
         <v>0.9364</v>
       </c>
       <c r="C2">
-        <v>0.9366</v>
+        <v>0.9365</v>
       </c>
     </row>
     <row r="3">
@@ -395,7 +395,7 @@
         <v>0.9862</v>
       </c>
       <c r="C3">
-        <v>0.9855</v>
+        <v>0.9856</v>
       </c>
     </row>
     <row r="4">
@@ -421,7 +421,7 @@
         <v>0.9902</v>
       </c>
       <c r="C5">
-        <v>0.9888</v>
+        <v>0.9887</v>
       </c>
     </row>
     <row r="6">
@@ -434,7 +434,7 @@
         <v>0.969</v>
       </c>
       <c r="C6">
-        <v>0.9641</v>
+        <v>0.964</v>
       </c>
     </row>
     <row r="7">
@@ -444,7 +444,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.9903999999999999</v>
+        <v>0.9903</v>
       </c>
       <c r="C7">
         <v>0.9947</v>
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.9693000000000001</v>
+        <v>0.9692</v>
       </c>
       <c r="C8">
         <v>0.9756</v>
@@ -473,7 +473,7 @@
         <v>0.9845</v>
       </c>
       <c r="C9">
-        <v>0.9827</v>
+        <v>0.9826</v>
       </c>
     </row>
     <row r="10">
@@ -496,10 +496,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.9634</v>
+        <v>0.9633</v>
       </c>
       <c r="C11">
-        <v>0.9654</v>
+        <v>0.9653</v>
       </c>
     </row>
     <row r="12">
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.9877</v>
+        <v>0.9876</v>
       </c>
       <c r="C13">
-        <v>0.9885</v>
+        <v>0.9883999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -538,7 +538,7 @@
         <v>0.7944</v>
       </c>
       <c r="C14">
-        <v>0.782</v>
+        <v>0.7823</v>
       </c>
     </row>
     <row r="15">
@@ -574,10 +574,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.9305</v>
+        <v>0.9304</v>
       </c>
       <c r="C17">
-        <v>0.9305</v>
+        <v>0.9304</v>
       </c>
     </row>
     <row r="18">
@@ -600,7 +600,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -627,10 +627,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.5111</v>
+        <v>0.269</v>
       </c>
       <c r="C2">
-        <v>0.655</v>
+        <v>0.3537</v>
       </c>
     </row>
     <row r="3">
@@ -640,10 +640,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.845</v>
+        <v>0.7837</v>
       </c>
       <c r="C3">
-        <v>0.8237</v>
+        <v>0.7854</v>
       </c>
     </row>
     <row r="4">
@@ -653,10 +653,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.8614000000000001</v>
+        <v>0.7786</v>
       </c>
       <c r="C4">
-        <v>0.7927999999999999</v>
+        <v>0.7485000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -666,10 +666,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.9866</v>
+        <v>0.9903</v>
       </c>
       <c r="C5">
-        <v>0.9902</v>
+        <v>0.9932</v>
       </c>
     </row>
     <row r="6">
@@ -679,10 +679,36 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.9752</v>
+        <v>0.9883</v>
       </c>
       <c r="C6">
-        <v>0.9871</v>
+        <v>0.9919</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Headline TRI exposure denominator: per-employee vs volume</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.8788</v>
+      </c>
+      <c r="C7">
+        <v>0.8482</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Headline TRI exposure denominator: per-employee vs per-regional-GDP</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.9679</v>
+      </c>
+      <c r="C8">
+        <v>0.9574</v>
       </c>
     </row>
   </sheetData>

--- a/Code and data/Final data/Sensitivity_Analysis.xlsx
+++ b/Code and data/Final data/Sensitivity_Analysis.xlsx
@@ -627,36 +627,36 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.269</v>
+        <v>0.1012</v>
       </c>
       <c r="C2">
-        <v>0.3537</v>
+        <v>0.2364</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Headline TRI norm: minmax vs log</t>
+          <t>Headline TRI norm: log vs minmax</t>
         </is>
       </c>
       <c r="B3">
-        <v>0.7837</v>
+        <v>0.782</v>
       </c>
       <c r="C3">
-        <v>0.7854</v>
+        <v>0.8075</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Headline TRI norm: minmax vs rank</t>
+          <t>Headline TRI norm: log vs rank</t>
         </is>
       </c>
       <c r="B4">
-        <v>0.7786</v>
+        <v>0.98</v>
       </c>
       <c r="C4">
-        <v>0.7485000000000001</v>
+        <v>0.9426</v>
       </c>
     </row>
     <row r="5">
@@ -666,10 +666,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.9903</v>
+        <v>0.9912</v>
       </c>
       <c r="C5">
-        <v>0.9932</v>
+        <v>0.9895</v>
       </c>
     </row>
     <row r="6">
@@ -679,10 +679,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.9883</v>
+        <v>0.9748</v>
       </c>
       <c r="C6">
-        <v>0.9919</v>
+        <v>0.9806</v>
       </c>
     </row>
     <row r="7">
@@ -692,10 +692,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.8788</v>
+        <v>0.7471</v>
       </c>
       <c r="C7">
-        <v>0.8482</v>
+        <v>0.8069</v>
       </c>
     </row>
     <row r="8">
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.9679</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="C8">
-        <v>0.9574</v>
+        <v>0.7556</v>
       </c>
     </row>
   </sheetData>
